--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487027_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487027_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.642</v>
+        <v>5.179</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9107</v>
+        <v>3.3291</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7313</v>
+        <v>1.8499</v>
       </c>
       <c r="G2" t="n">
         <v>3.0248</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2658</v>
+        <v>0.2712</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4457</v>
+        <v>-0.0272</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1799</v>
+        <v>0.2985</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7504</v>
+        <v>4.3375</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2559</v>
+        <v>3.6356</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4945</v>
+        <v>0.702</v>
       </c>
       <c r="G3" t="n">
         <v>4.2405</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0725</v>
+        <v>0.6596</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2171</v>
+        <v>0.1626</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2896</v>
+        <v>0.4971</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1786</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5122</v>
+        <v>2.7859</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9821</v>
+        <v>0.2447</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5301</v>
+        <v>2.5413</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2944</v>
+        <v>1.4419</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4232</v>
+        <v>1.9365</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1287</v>
+        <v>-0.4947</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6095</v>
+        <v>0.2994</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5306</v>
+        <v>1.6546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0789</v>
+        <v>-1.3552</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3151</v>
+        <v>1.1425</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1074</v>
+        <v>0.2819</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2077</v>
+        <v>0.8606</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5669</v>
+        <v>0.4611</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1858</v>
+        <v>0.2944</v>
       </c>
       <c r="U4" t="n">
-        <v>1.381</v>
+        <v>0.1667</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9384</v>
+        <v>-0.3491</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2402</v>
+        <v>-0.3491</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1304</v>
+        <v>2.1038</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1737</v>
+        <v>1.048</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3041</v>
+        <v>1.0558</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4419</v>
+        <v>2.2944</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9365</v>
+        <v>2.4232</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4947</v>
+        <v>-0.1287</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2994</v>
+        <v>2.6095</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6546</v>
+        <v>2.5306</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3552</v>
+        <v>0.0789</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1425</v>
+        <v>-0.3151</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2819</v>
+        <v>-0.1074</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8606</v>
+        <v>-0.2077</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2321</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1944</v>
+        <v>1.1585</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.124</v>
+        <v>0.2517</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0704</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3491</v>
+        <v>-0.9384</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3491</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ARAGONES NAVAIS</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1818</v>
+        <v>0.7119</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2204</v>
+        <v>0.9736</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4023</v>
+        <v>-0.2617</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7658</v>
+        <v>-0.9325</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.116</v>
+        <v>0.12</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6498</v>
+        <v>-1.0525</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3718</v>
+        <v>1.313</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6745</v>
+        <v>2.0897</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6974</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.394</v>
+        <v>-2.2456</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4415</v>
+        <v>-1.9697</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0475</v>
+        <v>-0.2759</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S6" t="n">
-        <v>1.769</v>
+        <v>0.9957</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.4492</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7696</v>
+        <v>0.5465</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1786</v>
+        <v>3.3182</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1786</v>
+        <v>3.3182</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>A. ARAGONES NAVAIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0405</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9465</v>
+        <v>-0.7822</v>
       </c>
       <c r="F7" t="n">
-        <v>0.094</v>
+        <v>1.2837</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9325</v>
+        <v>-1.7658</v>
       </c>
       <c r="H7" t="n">
-        <v>0.12</v>
+        <v>-1.116</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0525</v>
+        <v>-0.6498</v>
       </c>
       <c r="J7" t="n">
-        <v>1.313</v>
+        <v>-1.3718</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0897</v>
+        <v>-0.6745</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.6974</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2456</v>
+        <v>-0.394</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9697</v>
+        <v>-0.4415</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2759</v>
+        <v>0.0475</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.6694</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3243</v>
+        <v>1.0887</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4221</v>
+        <v>0.4377</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9022</v>
+        <v>0.651</v>
       </c>
       <c r="V7" t="n">
-        <v>3.3182</v>
+        <v>1.1786</v>
       </c>
       <c r="W7" t="n">
-        <v>3.3182</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6844</v>
+        <v>0.4727</v>
       </c>
       <c r="E8" t="n">
-        <v>0.983</v>
+        <v>0.801</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2987</v>
+        <v>-0.3283</v>
       </c>
       <c r="G8" t="n">
         <v>0.538</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3518</v>
+        <v>1.1401</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.6198</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5203</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5893</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8305</v>
+        <v>-2.5122</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2879</v>
+        <v>-2.2642</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5426</v>
+        <v>-0.248</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.016</v>
+        <v>-1.1213</v>
       </c>
       <c r="H9" t="n">
-        <v>0.289</v>
+        <v>0.2205</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.305</v>
+        <v>-1.3418</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3589</v>
+        <v>0.541</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8984</v>
+        <v>0.6069</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5395</v>
+        <v>-0.0659</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.375</v>
+        <v>-1.6623</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6094</v>
+        <v>-0.3863</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2345</v>
+        <v>-1.2759</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.6694</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6845</v>
+        <v>0.6625</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4333</v>
+        <v>0.275</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2512</v>
+        <v>0.3875</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8013</v>
+        <v>-2.7653</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4347</v>
+        <v>-1.1634</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3666</v>
+        <v>-1.6019</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1213</v>
+        <v>-0.016</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2205</v>
+        <v>0.289</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3418</v>
+        <v>-0.305</v>
       </c>
       <c r="J10" t="n">
-        <v>0.541</v>
+        <v>1.3589</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6069</v>
+        <v>1.8984</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0659</v>
+        <v>-0.5395</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6623</v>
+        <v>-1.375</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3863</v>
+        <v>-1.6094</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2759</v>
+        <v>0.2345</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0534</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q10" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3734</v>
+        <v>0.7497</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1045</v>
+        <v>0.5578</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2689</v>
+        <v>0.1919</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.4339</v>
+        <v>-7.2801</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.7721</v>
+        <v>-4.974</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6618</v>
+        <v>-2.3061</v>
       </c>
       <c r="G11" t="n">
         <v>-7.1637</v>
@@ -1312,13 +1312,13 @@
         <v>0.8214</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8245</v>
+        <v>0.3293</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6433</v>
+        <v>0.1548</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1813</v>
+        <v>0.1744</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.876000000000001</v>
+        <v>3.5347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1894000000000009</v>
+        <v>0.8482000000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>2.686600000000001</v>
+        <v>2.686699999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5402999999999984</v>
+        <v>0.5402999999999993</v>
       </c>
       <c r="H12" t="n">
-        <v>2.513300000000001</v>
+        <v>2.5133</v>
       </c>
       <c r="I12" t="n">
         <v>-1.973100000000001</v>
@@ -1390,16 +1390,16 @@
         <v>11.2938</v>
       </c>
       <c r="S12" t="n">
-        <v>6.857699999999999</v>
+        <v>7.5164</v>
       </c>
       <c r="T12" t="n">
-        <v>2.516999999999999</v>
+        <v>3.1758</v>
       </c>
       <c r="U12" t="n">
-        <v>4.3406</v>
+        <v>4.3407</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6119000000000001</v>
+        <v>0.6119</v>
       </c>
       <c r="W12" t="n">
         <v>5.8067</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6149</v>
+        <v>4.0577</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2165</v>
+        <v>3.3211</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3984</v>
+        <v>0.7366</v>
       </c>
       <c r="G13" t="n">
         <v>0.41</v>
@@ -1468,13 +1468,13 @@
         <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2584</v>
+        <v>-0.8156</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8177</v>
+        <v>-0.7131</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4407</v>
+        <v>-0.1025</v>
       </c>
       <c r="V13" t="n">
         <v>1.9992</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7112</v>
+        <v>1.9174</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0061</v>
+        <v>-0.1301</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7173</v>
+        <v>2.0475</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2723</v>
+        <v>1.4563</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3983</v>
+        <v>0.1037</v>
       </c>
       <c r="I14" t="n">
-        <v>0.874</v>
+        <v>1.3526</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2603</v>
+        <v>1.4081</v>
       </c>
       <c r="K14" t="n">
-        <v>3.063</v>
+        <v>0.6847</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1973</v>
+        <v>0.7234</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.988</v>
+        <v>0.0482</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6646</v>
+        <v>-0.581</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6766</v>
+        <v>0.6291</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0801</v>
+        <v>-1.2321</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2855</v>
+        <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1681</v>
+        <v>-0.3603</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1862</v>
+        <v>-0.3062</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0181</v>
+        <v>-0.0541</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5983000000000001</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5983000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6176</v>
+        <v>1.1568</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5485</v>
+        <v>-0.4245</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1661</v>
+        <v>1.5812</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4563</v>
+        <v>2.2723</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1037</v>
+        <v>1.3983</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3526</v>
+        <v>0.874</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4081</v>
+        <v>3.2603</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6847</v>
+        <v>3.063</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7234</v>
+        <v>0.1973</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0482</v>
+        <v>-0.988</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.581</v>
+        <v>-1.6646</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6291</v>
+        <v>0.6766</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2321</v>
+        <v>-3.0801</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0534</v>
+        <v>3.2855</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6601</v>
+        <v>-0.7226</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7246</v>
+        <v>-0.6046</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0645</v>
+        <v>-0.1179</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5983000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2672</v>
+        <v>1.0321</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4647</v>
+        <v>0.5405</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1974</v>
+        <v>0.4917</v>
       </c>
       <c r="G16" t="n">
-        <v>0.384</v>
+        <v>2.1641</v>
       </c>
       <c r="H16" t="n">
-        <v>1.197</v>
+        <v>-0.354</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8131</v>
+        <v>2.5181</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8599</v>
+        <v>3.6518</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5573</v>
+        <v>1.8103</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6974</v>
+        <v>1.8415</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4759</v>
+        <v>-1.4877</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3602</v>
+        <v>-2.1643</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1157</v>
+        <v>0.6766</v>
       </c>
       <c r="P16" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>2.8748</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6149</v>
+        <v>-1.5953</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3952</v>
+        <v>-1.0579</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2197</v>
+        <v>-0.5374</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1179</v>
+        <v>-0.3581</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1179</v>
+        <v>-0.3581</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0227</v>
+        <v>0.4608</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0175</v>
+        <v>0.5693</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0052</v>
+        <v>-0.1085</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1641</v>
+        <v>0.384</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.354</v>
+        <v>1.197</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5181</v>
+        <v>-0.8131</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6518</v>
+        <v>0.8599</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8103</v>
+        <v>1.5573</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8415</v>
+        <v>-0.6974</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4877</v>
+        <v>-0.4759</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.1643</v>
+        <v>-0.3602</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6766</v>
+        <v>-0.1157</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8748</v>
+        <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.6047</v>
+        <v>-0.4214</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5809</v>
+        <v>-0.2906</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0238</v>
+        <v>-0.1307</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3581</v>
+        <v>-0.1179</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3581</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0316</v>
+        <v>-0.3611</v>
       </c>
       <c r="E18" t="n">
-        <v>0.664</v>
+        <v>0.2456</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6956</v>
+        <v>-0.6067</v>
       </c>
       <c r="G18" t="n">
         <v>-0.517</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4854</v>
+        <v>0.1559</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5656</v>
+        <v>0.1472</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5885</v>
+        <v>-1.5292</v>
       </c>
       <c r="E19" t="n">
         <v>-1.7123</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1238</v>
+        <v>0.1831</v>
       </c>
       <c r="G19" t="n">
         <v>-1.291</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0922</v>
+        <v>-0.0329</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7873</v>
+        <v>-1.8622</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1</v>
+        <v>-1.2046</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6873</v>
+        <v>-0.6576</v>
       </c>
       <c r="G20" t="n">
         <v>-2.402</v>
@@ -2014,13 +2014,13 @@
         <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.7448</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4883</v>
+        <v>-0.5929</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1815</v>
+        <v>-0.1519</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3581</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3651</v>
+        <v>-1.8926</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.532</v>
+        <v>-1.4273</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8331</v>
+        <v>-0.4653</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9982</v>
@@ -2092,13 +2092,13 @@
         <v>2.6694</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0178</v>
+        <v>-0.5454</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4225</v>
+        <v>-0.3179</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5954</v>
+        <v>-0.2275</v>
       </c>
       <c r="V21" t="n">
         <v>0.2402</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3373</v>
+        <v>-4.461</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1505</v>
+        <v>-2.4643</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1868</v>
+        <v>-1.9967</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0187</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2569</v>
+        <v>-0.3807</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.159</v>
+        <v>-0.4728</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0979</v>
+        <v>0.0921</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4189</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.876199999999999</v>
+        <v>-1.481300000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6867</v>
+        <v>-2.6866</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1893999999999991</v>
+        <v>1.205299999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5401999999999993</v>
+        <v>-0.5402000000000002</v>
       </c>
       <c r="H23" t="n">
         <v>-2.5136</v>
@@ -2239,7 +2239,7 @@
         <v>2.1072</v>
       </c>
       <c r="P23" t="n">
-        <v>5.133599999999999</v>
+        <v>5.133600000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.2938</v>
@@ -2248,16 +2248,16 @@
         <v>16.4273</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.857600000000001</v>
+        <v>-5.4631</v>
       </c>
       <c r="T23" t="n">
         <v>-4.3405</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.5171</v>
+        <v>-1.1224</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6119000000000001</v>
+        <v>-0.6118999999999999</v>
       </c>
       <c r="W23" t="n">
         <v>5.194900000000001</v>
